--- a/Product_Source/液压货梯升降机链条式货物升降机工厂仓库装卸货平台提升机举升机/液压货梯升降机链条式货物升降机工厂仓库装卸货平台提升机举升机.xlsx
+++ b/Product_Source/液压货梯升降机链条式货物升降机工厂仓库装卸货平台提升机举升机/液压货梯升降机链条式货物升降机工厂仓库装卸货平台提升机举升机.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\Data\1688\液压货梯升降机链条式货物升降机工厂仓库装卸货平台提升机举升机\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\technological-trappist\Product_Source\液压货梯升降机链条式货物升降机工厂仓库装卸货平台提升机举升机\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9993EEFB-B685-4553-8127-1C015DBE76DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D802CB-58B1-4041-8B4C-D6DF16BC953A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>产品规格</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>设备自重</t>
-  </si>
-  <si>
-    <t>进货数量</t>
   </si>
   <si>
     <t>1T</t>
@@ -426,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
@@ -436,7 +433,7 @@
     <col min="12" max="12" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,42 +468,39 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2">
         <v>2000</v>
@@ -515,36 +509,36 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3">
         <v>2000</v>
